--- a/Assets/Data/DataTable/08_Buf_Table.xlsx
+++ b/Assets/Data/DataTable/08_Buf_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90667400-A460-420D-A7E7-F5BB122C67AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCAF9B8-5420-4506-B567-1269EE31460E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -418,7 +418,24 @@
 10: 속성 과부하 계수
 11: 받는 피해 증가
 12: 받는 피해 감소
-13: SP 소모량 증가</t>
+13: SP 소모량 증가
+14: 도발</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{A004C954-977A-4174-878C-4EC4F25E7E59}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>0: NONE
+1: Add
+2: Mul</t>
         </r>
       </text>
     </comment>
@@ -427,7 +444,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="95">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -758,10 +775,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>재적용 규칙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SP 증가 , 스피드, 공격력, 방어력, 치확, 치뎀, 카운터 데미지, 속성 게이지 효율, 속성 게이지 저항, 속성 과부하, 받는 데미지 증가, 받는 데미지 감소, SP 소모량 증가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -770,14 +783,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>refresh extend atack-&gt; 더 좋은 걸로 리프레쉬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>더하기, 곱하기 등</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Table_Buf</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -786,14 +791,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>지속 턴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>enum:Status_Key:NONE</t>
-  </si>
-  <si>
-    <t>enum:Status_Key:NONE</t>
+    <t>enum:Buf_Category:NONE</t>
+  </si>
+  <si>
+    <t>enum:Buf_Category:NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">보정 방식 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:Calculate_Mode</t>
+  </si>
+  <si>
+    <t>enum:Calculate_Mode</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -803,7 +815,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="179" formatCode="00"/>
+    <numFmt numFmtId="177" formatCode="00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1037,10 +1049,10 @@
     <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3338,13 +3350,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
+        <v>94</v>
+      </c>
       <c r="C14" t="s">
         <v>73</v>
       </c>
@@ -3696,20 +3711,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.875" style="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.625" customWidth="1"/>
+    <col min="6" max="6" width="19.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C1"/>
     </row>
@@ -3727,9 +3743,11 @@
         <v>76</v>
       </c>
       <c r="E2" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="22"/>
     </row>
     <row r="3" spans="1:8" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -3745,9 +3763,11 @@
         <v>58</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="29"/>
+        <v>90</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="1:8" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
@@ -3812,15 +3832,7 @@
         <v>83</v>
       </c>
       <c r="H11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -3828,20 +3840,12 @@
         <v>84</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G14" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G15" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
